--- a/IPCA.xlsx
+++ b/IPCA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\OneDrive\Documentos\TCC_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A8AE32-7609-48CE-818F-8E7301715ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677B6293-DD65-4B94-84E0-0E53FE764BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47E4BECD-C709-4E89-90ED-AD0720138F23}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>Data</t>
   </si>
@@ -273,12 +273,15 @@
   <si>
     <t>espectativa_inflacao</t>
   </si>
+  <si>
+    <t>meta_inflcao</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,8 +334,27 @@
       <name val="STXinwei"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,8 +403,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E9ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -416,6 +450,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -423,7 +468,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -470,6 +515,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2343,8 +2398,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62ADD837-DD13-4138-AFC0-053CA5B48DDD}">
-  <dimension ref="A1:X318"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y318"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
@@ -2370,9 +2425,10 @@
     <col min="22" max="22" width="21.6640625" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19.88671875" customWidth="1"/>
+    <col min="25" max="25" width="8.44140625" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2445,8 +2501,11 @@
       <c r="X1" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y1" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>36526</v>
       </c>
@@ -2499,8 +2558,11 @@
         <v>19</v>
       </c>
       <c r="X2" s="9"/>
-    </row>
-    <row r="3" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y2" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>36557</v>
       </c>
@@ -2553,8 +2615,11 @@
         <v>18.86</v>
       </c>
       <c r="X3" s="9"/>
-    </row>
-    <row r="4" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y3" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>36586</v>
       </c>
@@ -2607,8 +2672,11 @@
         <v>18.86</v>
       </c>
       <c r="X4" s="9"/>
-    </row>
-    <row r="5" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y4" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>36617</v>
       </c>
@@ -2661,8 +2729,11 @@
         <v>16.77</v>
       </c>
       <c r="X5" s="9"/>
-    </row>
-    <row r="6" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y5" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>36647</v>
       </c>
@@ -2715,8 +2786,11 @@
         <v>19.420000000000002</v>
       </c>
       <c r="X6" s="9"/>
-    </row>
-    <row r="7" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y6" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>36678</v>
       </c>
@@ -2769,8 +2843,11 @@
         <v>18.02</v>
       </c>
       <c r="X7" s="9"/>
-    </row>
-    <row r="8" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y7" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>36708</v>
       </c>
@@ -2823,8 +2900,11 @@
         <v>16.899999999999999</v>
       </c>
       <c r="X8" s="9"/>
-    </row>
-    <row r="9" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y8" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>36739</v>
       </c>
@@ -2877,8 +2957,11 @@
         <v>18.3</v>
       </c>
       <c r="X9" s="9"/>
-    </row>
-    <row r="10" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y9" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>36770</v>
       </c>
@@ -2931,8 +3014,11 @@
         <v>15.66</v>
       </c>
       <c r="X10" s="9"/>
-    </row>
-    <row r="11" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y10" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>36800</v>
       </c>
@@ -2985,8 +3071,11 @@
         <v>16.63</v>
       </c>
       <c r="X11" s="9"/>
-    </row>
-    <row r="12" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y11" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>36831</v>
       </c>
@@ -3039,8 +3128,11 @@
         <v>15.66</v>
       </c>
       <c r="X12" s="9"/>
-    </row>
-    <row r="13" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y12" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>36861</v>
       </c>
@@ -3093,8 +3185,11 @@
         <v>15.39</v>
       </c>
       <c r="X13" s="9"/>
-    </row>
-    <row r="14" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y13" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>36892</v>
       </c>
@@ -3147,8 +3242,11 @@
         <v>16.350000000000001</v>
       </c>
       <c r="X14" s="9"/>
-    </row>
-    <row r="15" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y14" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>36923</v>
       </c>
@@ -3201,8 +3299,11 @@
         <v>12.95</v>
       </c>
       <c r="X15" s="9"/>
-    </row>
-    <row r="16" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y15" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>36951</v>
       </c>
@@ -3255,8 +3356,11 @@
         <v>16.21</v>
       </c>
       <c r="X16" s="9"/>
-    </row>
-    <row r="17" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y16" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>36982</v>
       </c>
@@ -3309,8 +3413,11 @@
         <v>15.25</v>
       </c>
       <c r="X17" s="9"/>
-    </row>
-    <row r="18" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y17" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>37012</v>
       </c>
@@ -3363,8 +3470,11 @@
         <v>17.32</v>
       </c>
       <c r="X18" s="9"/>
-    </row>
-    <row r="19" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y18" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>37043</v>
       </c>
@@ -3417,8 +3527,11 @@
         <v>16.350000000000001</v>
       </c>
       <c r="X19" s="9"/>
-    </row>
-    <row r="20" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y19" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>37073</v>
       </c>
@@ -3473,8 +3586,11 @@
       <c r="X20" s="8">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y20" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>37104</v>
       </c>
@@ -3529,8 +3645,11 @@
       <c r="X21" s="10">
         <v>6.57</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y21" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>37135</v>
       </c>
@@ -3585,8 +3704,11 @@
       <c r="X22" s="8">
         <v>6.53</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y22" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>37165</v>
       </c>
@@ -3641,8 +3763,11 @@
       <c r="X23" s="10">
         <v>6.49</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y23" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>37196</v>
       </c>
@@ -3697,8 +3822,11 @@
       <c r="X24" s="15">
         <v>5.57</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y24" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>37226</v>
       </c>
@@ -3753,8 +3881,11 @@
       <c r="X25" s="10">
         <v>4.84</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y25" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>37257</v>
       </c>
@@ -3814,8 +3945,11 @@
       <c r="X26" s="8">
         <v>4.76</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y26" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>37288</v>
       </c>
@@ -3875,8 +4009,11 @@
       <c r="X27" s="10">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y27" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>37316</v>
       </c>
@@ -3936,8 +4073,11 @@
       <c r="X28" s="8">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y28" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>37347</v>
       </c>
@@ -3997,8 +4137,11 @@
       <c r="X29" s="10">
         <v>4.9000000000000004</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y29" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>37377</v>
       </c>
@@ -4058,8 +4201,11 @@
       <c r="X30" s="8">
         <v>4.37</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y30" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>37408</v>
       </c>
@@ -4119,8 +4265,11 @@
       <c r="X31" s="10">
         <v>4.57</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y31" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>37438</v>
       </c>
@@ -4180,8 +4329,11 @@
       <c r="X32" s="8">
         <v>5.08</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y32" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>37469</v>
       </c>
@@ -4241,8 +4393,11 @@
       <c r="X33" s="10">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y33" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>37500</v>
       </c>
@@ -4302,8 +4457,11 @@
       <c r="X34" s="8">
         <v>6.28</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y34" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>37530</v>
       </c>
@@ -4363,8 +4521,11 @@
       <c r="X35" s="10">
         <v>8.94</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y35" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>37561</v>
       </c>
@@ -4424,8 +4585,11 @@
       <c r="X36" s="8">
         <v>12.47</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y36" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>37591</v>
       </c>
@@ -4497,8 +4661,11 @@
       <c r="X37" s="10">
         <v>13.24</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y37" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37622</v>
       </c>
@@ -4578,8 +4745,11 @@
       <c r="X38" s="8">
         <v>11.72</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y38" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>37653</v>
       </c>
@@ -4659,8 +4829,11 @@
       <c r="X39" s="10">
         <v>11.07</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y39" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>37681</v>
       </c>
@@ -4740,8 +4913,11 @@
       <c r="X40" s="8">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y40" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>37712</v>
       </c>
@@ -4821,8 +4997,11 @@
       <c r="X41" s="10">
         <v>9.18</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y41" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>37742</v>
       </c>
@@ -4902,8 +5081,11 @@
       <c r="X42" s="8">
         <v>8.23</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y42" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>37773</v>
       </c>
@@ -4983,8 +5165,11 @@
       <c r="X43" s="10">
         <v>7.08</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y43" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>37803</v>
       </c>
@@ -5064,8 +5249,11 @@
       <c r="X44" s="8">
         <v>6.39</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y44" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>37834</v>
       </c>
@@ -5145,8 +5333,11 @@
       <c r="X45" s="10">
         <v>6.32</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y45" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>37865</v>
       </c>
@@ -5226,8 +5417,11 @@
       <c r="X46" s="8">
         <v>6.56</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y46" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>37895</v>
       </c>
@@ -5307,8 +5501,11 @@
       <c r="X47" s="10">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y47" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>37926</v>
       </c>
@@ -5388,8 +5585,11 @@
       <c r="X48" s="8">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y48" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>37956</v>
       </c>
@@ -5469,8 +5669,11 @@
       <c r="X49" s="10">
         <v>5.92</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y49" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>37987</v>
       </c>
@@ -5550,8 +5753,11 @@
       <c r="X50" s="8">
         <v>6.01</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y50" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>38018</v>
       </c>
@@ -5631,8 +5837,11 @@
       <c r="X51" s="10">
         <v>5.74</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y51" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>38047</v>
       </c>
@@ -5712,8 +5921,11 @@
       <c r="X52" s="8">
         <v>5.54</v>
       </c>
-    </row>
-    <row r="53" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y52" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>38078</v>
       </c>
@@ -5793,8 +6005,11 @@
       <c r="X53" s="10">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="54" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y53" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>38108</v>
       </c>
@@ -5874,8 +6089,11 @@
       <c r="X54" s="8">
         <v>5.98</v>
       </c>
-    </row>
-    <row r="55" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y54" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>38139</v>
       </c>
@@ -5955,8 +6173,11 @@
       <c r="X55" s="10">
         <v>6.33</v>
       </c>
-    </row>
-    <row r="56" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y55" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>38169</v>
       </c>
@@ -6036,8 +6257,11 @@
       <c r="X56" s="8">
         <v>6.36</v>
       </c>
-    </row>
-    <row r="57" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y56" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>38200</v>
       </c>
@@ -6117,8 +6341,11 @@
       <c r="X57" s="10">
         <v>6.27</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y57" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>38231</v>
       </c>
@@ -6198,8 +6425,11 @@
       <c r="X58" s="8">
         <v>6.24</v>
       </c>
-    </row>
-    <row r="59" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y58" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>38261</v>
       </c>
@@ -6279,8 +6509,11 @@
       <c r="X59" s="10">
         <v>6.22</v>
       </c>
-    </row>
-    <row r="60" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y59" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>38292</v>
       </c>
@@ -6360,8 +6593,11 @@
       <c r="X60" s="8">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="61" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y60" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>38322</v>
       </c>
@@ -6441,8 +6677,11 @@
       <c r="X61" s="10">
         <v>6.08</v>
       </c>
-    </row>
-    <row r="62" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y61" s="20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>38353</v>
       </c>
@@ -6522,8 +6761,11 @@
       <c r="X62" s="8">
         <v>5.74</v>
       </c>
-    </row>
-    <row r="63" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y62" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>38384</v>
       </c>
@@ -6603,8 +6845,11 @@
       <c r="X63" s="10">
         <v>5.61</v>
       </c>
-    </row>
-    <row r="64" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y63" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>38412</v>
       </c>
@@ -6684,8 +6929,11 @@
       <c r="X64" s="8">
         <v>5.67</v>
       </c>
-    </row>
-    <row r="65" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y64" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>38443</v>
       </c>
@@ -6765,8 +7013,11 @@
       <c r="X65" s="10">
         <v>5.87</v>
       </c>
-    </row>
-    <row r="66" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y65" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>38473</v>
       </c>
@@ -6846,8 +7097,11 @@
       <c r="X66" s="8">
         <v>5.46</v>
       </c>
-    </row>
-    <row r="67" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y66" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>38504</v>
       </c>
@@ -6927,8 +7181,11 @@
       <c r="X67" s="10">
         <v>4.8499999999999996</v>
       </c>
-    </row>
-    <row r="68" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y67" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>38534</v>
       </c>
@@ -7008,8 +7265,11 @@
       <c r="X68" s="8">
         <v>4.8600000000000003</v>
       </c>
-    </row>
-    <row r="69" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y68" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>38565</v>
       </c>
@@ -7089,8 +7349,11 @@
       <c r="X69" s="10">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="70" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y69" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>38596</v>
       </c>
@@ -7170,8 +7433,11 @@
       <c r="X70" s="8">
         <v>4.74</v>
       </c>
-    </row>
-    <row r="71" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y70" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>38626</v>
       </c>
@@ -7251,8 +7517,11 @@
       <c r="X71" s="10">
         <v>4.7300000000000004</v>
       </c>
-    </row>
-    <row r="72" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y71" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>38657</v>
       </c>
@@ -7332,8 +7601,11 @@
       <c r="X72" s="8">
         <v>4.6100000000000003</v>
       </c>
-    </row>
-    <row r="73" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y72" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>38687</v>
       </c>
@@ -7413,8 +7685,11 @@
       <c r="X73" s="10">
         <v>4.46</v>
       </c>
-    </row>
-    <row r="74" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y73" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>38718</v>
       </c>
@@ -7494,8 +7769,11 @@
       <c r="X74" s="8">
         <v>4.62</v>
       </c>
-    </row>
-    <row r="75" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y74" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>38749</v>
       </c>
@@ -7575,8 +7853,11 @@
       <c r="X75" s="10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="76" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y75" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>38777</v>
       </c>
@@ -7656,8 +7937,11 @@
       <c r="X76" s="8">
         <v>4.3099999999999996</v>
       </c>
-    </row>
-    <row r="77" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y76" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>38808</v>
       </c>
@@ -7737,8 +8021,11 @@
       <c r="X77" s="10">
         <v>4.0599999999999996</v>
       </c>
-    </row>
-    <row r="78" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y77" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>38838</v>
       </c>
@@ -7818,8 +8105,11 @@
       <c r="X78" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="79" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y78" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>38869</v>
       </c>
@@ -7899,8 +8189,11 @@
       <c r="X79" s="10">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="80" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y79" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>38899</v>
       </c>
@@ -7980,8 +8273,11 @@
       <c r="X80" s="8">
         <v>4.28</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y80" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>38930</v>
       </c>
@@ -8061,8 +8357,11 @@
       <c r="X81" s="10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="82" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y81" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>38961</v>
       </c>
@@ -8142,8 +8441,11 @@
       <c r="X82" s="8">
         <v>3.93</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y82" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>38991</v>
       </c>
@@ -8223,8 +8525,11 @@
       <c r="X83" s="10">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y83" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
         <v>39022</v>
       </c>
@@ -8304,8 +8609,11 @@
       <c r="X84" s="8">
         <v>4.1399999999999997</v>
       </c>
-    </row>
-    <row r="85" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y84" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
         <v>39052</v>
       </c>
@@ -8385,8 +8693,11 @@
       <c r="X85" s="10">
         <v>4.08</v>
       </c>
-    </row>
-    <row r="86" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y85" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>39083</v>
       </c>
@@ -8466,8 +8777,11 @@
       <c r="X86" s="8">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="87" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y86" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>39114</v>
       </c>
@@ -8547,8 +8861,11 @@
       <c r="X87" s="10">
         <v>3.81</v>
       </c>
-    </row>
-    <row r="88" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y87" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>39142</v>
       </c>
@@ -8628,8 +8945,11 @@
       <c r="X88" s="8">
         <v>3.74</v>
       </c>
-    </row>
-    <row r="89" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y88" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>39173</v>
       </c>
@@ -8709,8 +9029,11 @@
       <c r="X89" s="10">
         <v>3.47</v>
       </c>
-    </row>
-    <row r="90" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y89" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>39203</v>
       </c>
@@ -8790,8 +9113,11 @@
       <c r="X90" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="91" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y90" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>39234</v>
       </c>
@@ -8871,8 +9197,11 @@
       <c r="X91" s="10">
         <v>3.47</v>
       </c>
-    </row>
-    <row r="92" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y91" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>39264</v>
       </c>
@@ -8952,8 +9281,11 @@
       <c r="X92" s="8">
         <v>3.55</v>
       </c>
-    </row>
-    <row r="93" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y92" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>39295</v>
       </c>
@@ -9033,8 +9365,11 @@
       <c r="X93" s="10">
         <v>3.83</v>
       </c>
-    </row>
-    <row r="94" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y93" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
         <v>39326</v>
       </c>
@@ -9114,8 +9449,11 @@
       <c r="X94" s="8">
         <v>3.75</v>
       </c>
-    </row>
-    <row r="95" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y94" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>39356</v>
       </c>
@@ -9195,8 +9533,11 @@
       <c r="X95" s="10">
         <v>3.71</v>
       </c>
-    </row>
-    <row r="96" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y95" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
         <v>39387</v>
       </c>
@@ -9276,8 +9617,11 @@
       <c r="X96" s="8">
         <v>3.85</v>
       </c>
-    </row>
-    <row r="97" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y96" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
         <v>39417</v>
       </c>
@@ -9357,8 +9701,11 @@
       <c r="X97" s="10">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="98" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y97" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>39448</v>
       </c>
@@ -9438,8 +9785,11 @@
       <c r="X98" s="8">
         <v>4.4400000000000004</v>
       </c>
-    </row>
-    <row r="99" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y98" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>39479</v>
       </c>
@@ -9519,8 +9869,11 @@
       <c r="X99" s="10">
         <v>4.28</v>
       </c>
-    </row>
-    <row r="100" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y99" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
         <v>39508</v>
       </c>
@@ -9600,8 +9953,11 @@
       <c r="X100" s="8">
         <v>4.3600000000000003</v>
       </c>
-    </row>
-    <row r="101" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y100" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
         <v>39539</v>
       </c>
@@ -9681,8 +10037,11 @@
       <c r="X101" s="10">
         <v>4.5599999999999996</v>
       </c>
-    </row>
-    <row r="102" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y101" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
         <v>39569</v>
       </c>
@@ -9762,8 +10121,11 @@
       <c r="X102" s="8">
         <v>5.08</v>
       </c>
-    </row>
-    <row r="103" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y102" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
         <v>39600</v>
       </c>
@@ -9843,8 +10205,11 @@
       <c r="X103" s="10">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="104" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y103" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
         <v>39630</v>
       </c>
@@ -9924,8 +10289,11 @@
       <c r="X104" s="8">
         <v>5.49</v>
       </c>
-    </row>
-    <row r="105" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y104" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
         <v>39661</v>
       </c>
@@ -10005,8 +10373,11 @@
       <c r="X105" s="10">
         <v>5.16</v>
       </c>
-    </row>
-    <row r="106" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y105" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
         <v>39692</v>
       </c>
@@ -10086,8 +10457,11 @@
       <c r="X106" s="8">
         <v>5.01</v>
       </c>
-    </row>
-    <row r="107" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y106" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
         <v>39722</v>
       </c>
@@ -10167,8 +10541,11 @@
       <c r="X107" s="10">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="108" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y107" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
         <v>39753</v>
       </c>
@@ -10248,8 +10625,11 @@
       <c r="X108" s="8">
         <v>5.45</v>
       </c>
-    </row>
-    <row r="109" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y108" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
         <v>39783</v>
       </c>
@@ -10329,8 +10709,11 @@
       <c r="X109" s="10">
         <v>4.93</v>
       </c>
-    </row>
-    <row r="110" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y109" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
         <v>39814</v>
       </c>
@@ -10410,8 +10793,11 @@
       <c r="X110" s="8">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="111" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y110" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
         <v>39845</v>
       </c>
@@ -10491,8 +10877,11 @@
       <c r="X111" s="10">
         <v>4.57</v>
       </c>
-    </row>
-    <row r="112" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y111" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
         <v>39873</v>
       </c>
@@ -10572,8 +10961,11 @@
       <c r="X112" s="8">
         <v>4.1399999999999997</v>
       </c>
-    </row>
-    <row r="113" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y112" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
         <v>39904</v>
       </c>
@@ -10653,8 +11045,11 @@
       <c r="X113" s="10">
         <v>4.21</v>
       </c>
-    </row>
-    <row r="114" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y113" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
         <v>39934</v>
       </c>
@@ -10734,8 +11129,11 @@
       <c r="X114" s="8">
         <v>4.1399999999999997</v>
       </c>
-    </row>
-    <row r="115" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y114" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
         <v>39965</v>
       </c>
@@ -10815,8 +11213,11 @@
       <c r="X115" s="10">
         <v>4.0599999999999996</v>
       </c>
-    </row>
-    <row r="116" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y115" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
         <v>39995</v>
       </c>
@@ -10896,8 +11297,11 @@
       <c r="X116" s="8">
         <v>4.09</v>
       </c>
-    </row>
-    <row r="117" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y116" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
         <v>40026</v>
       </c>
@@ -10977,8 +11381,11 @@
       <c r="X117" s="10">
         <v>3.97</v>
       </c>
-    </row>
-    <row r="118" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y117" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
         <v>40057</v>
       </c>
@@ -11058,8 +11465,11 @@
       <c r="X118" s="8">
         <v>4.1900000000000004</v>
       </c>
-    </row>
-    <row r="119" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y118" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
         <v>40087</v>
       </c>
@@ -11139,8 +11549,11 @@
       <c r="X119" s="10">
         <v>4.32</v>
       </c>
-    </row>
-    <row r="120" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y119" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
         <v>40118</v>
       </c>
@@ -11220,8 +11633,11 @@
       <c r="X120" s="8">
         <v>4.3499999999999996</v>
       </c>
-    </row>
-    <row r="121" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y120" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
         <v>40148</v>
       </c>
@@ -11301,8 +11717,11 @@
       <c r="X121" s="10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="122" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y121" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>40179</v>
       </c>
@@ -11382,8 +11801,11 @@
       <c r="X122" s="8">
         <v>4.68</v>
       </c>
-    </row>
-    <row r="123" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y122" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
         <v>40210</v>
       </c>
@@ -11463,8 +11885,11 @@
       <c r="X123" s="10">
         <v>4.66</v>
       </c>
-    </row>
-    <row r="124" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y123" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
         <v>40238</v>
       </c>
@@ -11544,8 +11969,11 @@
       <c r="X124" s="8">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="125" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y124" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
         <v>40269</v>
       </c>
@@ -11625,8 +12053,11 @@
       <c r="X125" s="10">
         <v>4.8600000000000003</v>
       </c>
-    </row>
-    <row r="126" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y125" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
         <v>40299</v>
       </c>
@@ -11706,8 +12137,11 @@
       <c r="X126" s="8">
         <v>4.88</v>
       </c>
-    </row>
-    <row r="127" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y126" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
         <v>40330</v>
       </c>
@@ -11787,8 +12221,11 @@
       <c r="X127" s="10">
         <v>4.74</v>
       </c>
-    </row>
-    <row r="128" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y127" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
         <v>40360</v>
       </c>
@@ -11868,8 +12305,11 @@
       <c r="X128" s="8">
         <v>4.82</v>
       </c>
-    </row>
-    <row r="129" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y128" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
         <v>40391</v>
       </c>
@@ -11949,8 +12389,11 @@
       <c r="X129" s="10">
         <v>4.9800000000000004</v>
       </c>
-    </row>
-    <row r="130" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y129" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
         <v>40422</v>
       </c>
@@ -12030,8 +12473,11 @@
       <c r="X130" s="8">
         <v>5.31</v>
       </c>
-    </row>
-    <row r="131" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y130" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
         <v>40452</v>
       </c>
@@ -12111,8 +12557,11 @@
       <c r="X131" s="10">
         <v>5.42</v>
       </c>
-    </row>
-    <row r="132" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y131" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
         <v>40483</v>
       </c>
@@ -12192,8 +12641,11 @@
       <c r="X132" s="8">
         <v>5.61</v>
       </c>
-    </row>
-    <row r="133" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y132" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
         <v>40513</v>
       </c>
@@ -12273,8 +12725,11 @@
       <c r="X133" s="10">
         <v>5.52</v>
       </c>
-    </row>
-    <row r="134" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y133" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
         <v>40544</v>
       </c>
@@ -12354,8 +12809,11 @@
       <c r="X134" s="8">
         <v>5.67</v>
       </c>
-    </row>
-    <row r="135" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y134" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
         <v>40575</v>
       </c>
@@ -12435,8 +12893,11 @@
       <c r="X135" s="10">
         <v>5.61</v>
       </c>
-    </row>
-    <row r="136" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y135" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
         <v>40603</v>
       </c>
@@ -12516,8 +12977,11 @@
       <c r="X136" s="8">
         <v>5.61</v>
       </c>
-    </row>
-    <row r="137" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y136" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
         <v>40634</v>
       </c>
@@ -12597,8 +13061,11 @@
       <c r="X137" s="10">
         <v>4.8600000000000003</v>
       </c>
-    </row>
-    <row r="138" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y137" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
         <v>40664</v>
       </c>
@@ -12678,8 +13145,11 @@
       <c r="X138" s="8">
         <v>4.88</v>
       </c>
-    </row>
-    <row r="139" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y138" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -12759,8 +13229,11 @@
       <c r="X139" s="10">
         <v>4.74</v>
       </c>
-    </row>
-    <row r="140" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y139" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
         <v>40725</v>
       </c>
@@ -12840,8 +13313,11 @@
       <c r="X140" s="8">
         <v>5.35</v>
       </c>
-    </row>
-    <row r="141" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y140" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
         <v>40756</v>
       </c>
@@ -12921,8 +13397,11 @@
       <c r="X141" s="10">
         <v>5.47</v>
       </c>
-    </row>
-    <row r="142" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y141" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
         <v>40787</v>
       </c>
@@ -13002,8 +13481,11 @@
       <c r="X142" s="8">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="143" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y142" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
         <v>40817</v>
       </c>
@@ -13083,8 +13565,11 @@
       <c r="X143" s="10">
         <v>5.56</v>
       </c>
-    </row>
-    <row r="144" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y143" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
         <v>40848</v>
       </c>
@@ -13164,8 +13649,11 @@
       <c r="X144" s="8">
         <v>5.53</v>
       </c>
-    </row>
-    <row r="145" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y144" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
         <v>40878</v>
       </c>
@@ -13245,8 +13733,11 @@
       <c r="X145" s="10">
         <v>5.35</v>
       </c>
-    </row>
-    <row r="146" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y145" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
         <v>40909</v>
       </c>
@@ -13326,8 +13817,11 @@
       <c r="X146" s="8">
         <v>5.3</v>
       </c>
-    </row>
-    <row r="147" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y146" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
         <v>40940</v>
       </c>
@@ -13407,8 +13901,11 @@
       <c r="X147" s="10">
         <v>5.26</v>
       </c>
-    </row>
-    <row r="148" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y147" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
         <v>40969</v>
       </c>
@@ -13488,8 +13985,11 @@
       <c r="X148" s="8">
         <v>5.43</v>
       </c>
-    </row>
-    <row r="149" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y148" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
         <v>41000</v>
       </c>
@@ -13569,8 +14069,11 @@
       <c r="X149" s="10">
         <v>5.57</v>
       </c>
-    </row>
-    <row r="150" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y149" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
         <v>41030</v>
       </c>
@@ -13650,8 +14153,11 @@
       <c r="X150" s="8">
         <v>5.52</v>
       </c>
-    </row>
-    <row r="151" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y150" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
         <v>41061</v>
       </c>
@@ -13731,8 +14237,11 @@
       <c r="X151" s="10">
         <v>5.38</v>
       </c>
-    </row>
-    <row r="152" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y151" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
         <v>41091</v>
       </c>
@@ -13812,8 +14321,11 @@
       <c r="X152" s="8">
         <v>5.58</v>
       </c>
-    </row>
-    <row r="153" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y152" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
         <v>41122</v>
       </c>
@@ -13893,8 +14405,11 @@
       <c r="X153" s="10">
         <v>5.68</v>
       </c>
-    </row>
-    <row r="154" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y153" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
         <v>41153</v>
       </c>
@@ -13974,8 +14489,11 @@
       <c r="X154" s="8">
         <v>5.64</v>
       </c>
-    </row>
-    <row r="155" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y154" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
         <v>41183</v>
       </c>
@@ -14055,8 +14573,11 @@
       <c r="X155" s="10">
         <v>5.47</v>
       </c>
-    </row>
-    <row r="156" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y155" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
         <v>41214</v>
       </c>
@@ -14136,8 +14657,11 @@
       <c r="X156" s="8">
         <v>5.36</v>
       </c>
-    </row>
-    <row r="157" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y156" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
         <v>41244</v>
       </c>
@@ -14217,8 +14741,11 @@
       <c r="X157" s="10">
         <v>5.63</v>
       </c>
-    </row>
-    <row r="158" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y157" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
         <v>41275</v>
       </c>
@@ -14298,8 +14825,11 @@
       <c r="X158" s="8">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="159" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y158" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
         <v>41306</v>
       </c>
@@ -14379,8 +14909,11 @@
       <c r="X159" s="10">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="160" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y159" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
         <v>41334</v>
       </c>
@@ -14460,8 +14993,11 @@
       <c r="X160" s="8">
         <v>5.53</v>
       </c>
-    </row>
-    <row r="161" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y160" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
         <v>41365</v>
       </c>
@@ -14541,8 +15077,11 @@
       <c r="X161" s="10">
         <v>5.56</v>
       </c>
-    </row>
-    <row r="162" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y161" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
         <v>41395</v>
       </c>
@@ -14622,8 +15161,11 @@
       <c r="X162" s="8">
         <v>5.62</v>
       </c>
-    </row>
-    <row r="163" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y162" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
         <v>41426</v>
       </c>
@@ -14703,8 +15245,11 @@
       <c r="X163" s="10">
         <v>5.74</v>
       </c>
-    </row>
-    <row r="164" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y163" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
         <v>41456</v>
       </c>
@@ -14784,8 +15329,11 @@
       <c r="X164" s="8">
         <v>5.66</v>
       </c>
-    </row>
-    <row r="165" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y164" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
         <v>41487</v>
       </c>
@@ -14865,8 +15413,11 @@
       <c r="X165" s="10">
         <v>6.06</v>
       </c>
-    </row>
-    <row r="166" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y165" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
         <v>41518</v>
       </c>
@@ -14946,8 +15497,11 @@
       <c r="X166" s="8">
         <v>6.16</v>
       </c>
-    </row>
-    <row r="167" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y166" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
         <v>41548</v>
       </c>
@@ -15027,8 +15581,11 @@
       <c r="X167" s="10">
         <v>6.25</v>
       </c>
-    </row>
-    <row r="168" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y167" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
         <v>41579</v>
       </c>
@@ -15108,8 +15665,11 @@
       <c r="X168" s="8">
         <v>6.14</v>
       </c>
-    </row>
-    <row r="169" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y168" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
         <v>41609</v>
       </c>
@@ -15189,8 +15749,11 @@
       <c r="X169" s="10">
         <v>6.11</v>
       </c>
-    </row>
-    <row r="170" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y169" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
         <v>41640</v>
       </c>
@@ -15270,8 +15833,11 @@
       <c r="X170" s="8">
         <v>6.02</v>
       </c>
-    </row>
-    <row r="171" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y170" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
         <v>41671</v>
       </c>
@@ -15351,8 +15917,11 @@
       <c r="X171" s="10">
         <v>6.17</v>
       </c>
-    </row>
-    <row r="172" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y171" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
         <v>41699</v>
       </c>
@@ -15432,8 +16001,11 @@
       <c r="X172" s="8">
         <v>6.42</v>
       </c>
-    </row>
-    <row r="173" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y172" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
         <v>41730</v>
       </c>
@@ -15513,8 +16085,11 @@
       <c r="X173" s="10">
         <v>6.22</v>
       </c>
-    </row>
-    <row r="174" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y173" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
         <v>41760</v>
       </c>
@@ -15594,8 +16169,11 @@
       <c r="X174" s="8">
         <v>6.03</v>
       </c>
-    </row>
-    <row r="175" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y174" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
         <v>41791</v>
       </c>
@@ -15675,8 +16253,11 @@
       <c r="X175" s="10">
         <v>6.01</v>
       </c>
-    </row>
-    <row r="176" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y175" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
         <v>41821</v>
       </c>
@@ -15756,8 +16337,11 @@
       <c r="X176" s="8">
         <v>5.95</v>
       </c>
-    </row>
-    <row r="177" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y176" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
         <v>41852</v>
       </c>
@@ -15837,8 +16421,11 @@
       <c r="X177" s="10">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="178" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y177" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
         <v>41883</v>
       </c>
@@ -15918,8 +16505,11 @@
       <c r="X178" s="8">
         <v>6.33</v>
       </c>
-    </row>
-    <row r="179" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y178" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
         <v>41913</v>
       </c>
@@ -15999,8 +16589,11 @@
       <c r="X179" s="10">
         <v>6.41</v>
       </c>
-    </row>
-    <row r="180" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y179" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
         <v>41944</v>
       </c>
@@ -16080,8 +16673,11 @@
       <c r="X180" s="8">
         <v>6.56</v>
       </c>
-    </row>
-    <row r="181" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y180" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
         <v>41974</v>
       </c>
@@ -16161,8 +16757,11 @@
       <c r="X181" s="10">
         <v>6.73</v>
       </c>
-    </row>
-    <row r="182" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y181" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
         <v>42005</v>
       </c>
@@ -16242,8 +16841,11 @@
       <c r="X182" s="8">
         <v>6.97</v>
       </c>
-    </row>
-    <row r="183" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y182" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
         <v>42036</v>
       </c>
@@ -16323,8 +16925,11 @@
       <c r="X183" s="10">
         <v>6.88</v>
       </c>
-    </row>
-    <row r="184" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y183" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
         <v>42064</v>
       </c>
@@ -16404,8 +17009,11 @@
       <c r="X184" s="8">
         <v>7.01</v>
       </c>
-    </row>
-    <row r="185" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y184" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
         <v>42095</v>
       </c>
@@ -16485,8 +17093,11 @@
       <c r="X185" s="10">
         <v>6.17</v>
       </c>
-    </row>
-    <row r="186" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y185" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
         <v>42125</v>
       </c>
@@ -16566,8 +17177,11 @@
       <c r="X186" s="8">
         <v>6.11</v>
       </c>
-    </row>
-    <row r="187" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y186" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
         <v>42156</v>
       </c>
@@ -16647,8 +17261,11 @@
       <c r="X187" s="10">
         <v>6.38</v>
       </c>
-    </row>
-    <row r="188" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y187" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
         <v>42186</v>
       </c>
@@ -16728,8 +17345,11 @@
       <c r="X188" s="8">
         <v>5.98</v>
       </c>
-    </row>
-    <row r="189" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y188" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
         <v>42217</v>
       </c>
@@ -16809,8 +17429,11 @@
       <c r="X189" s="10">
         <v>5.66</v>
       </c>
-    </row>
-    <row r="190" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y189" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
         <v>42248</v>
       </c>
@@ -16890,8 +17513,11 @@
       <c r="X190" s="8">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="191" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y190" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
         <v>42278</v>
       </c>
@@ -16971,8 +17597,11 @@
       <c r="X191" s="10">
         <v>6.72</v>
       </c>
-    </row>
-    <row r="192" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y191" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
         <v>42309</v>
       </c>
@@ -17052,8 +17681,11 @@
       <c r="X192" s="8">
         <v>7.16</v>
       </c>
-    </row>
-    <row r="193" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y192" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
         <v>42339</v>
       </c>
@@ -17133,8 +17765,11 @@
       <c r="X193" s="10">
         <v>7.19</v>
       </c>
-    </row>
-    <row r="194" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y193" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
         <v>42370</v>
       </c>
@@ -17214,8 +17849,11 @@
       <c r="X194" s="8">
         <v>7.29</v>
       </c>
-    </row>
-    <row r="195" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y194" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
         <v>42401</v>
       </c>
@@ -17295,8 +17933,11 @@
       <c r="X195" s="10">
         <v>7.01</v>
       </c>
-    </row>
-    <row r="196" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y195" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
         <v>42430</v>
       </c>
@@ -17376,8 +18017,11 @@
       <c r="X196" s="8">
         <v>6.52</v>
       </c>
-    </row>
-    <row r="197" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y196" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
         <v>42461</v>
       </c>
@@ -17457,8 +18101,11 @@
       <c r="X197" s="10">
         <v>6.21</v>
       </c>
-    </row>
-    <row r="198" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y197" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
         <v>42491</v>
       </c>
@@ -17538,8 +18185,11 @@
       <c r="X198" s="8">
         <v>6.17</v>
       </c>
-    </row>
-    <row r="199" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y198" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
         <v>42522</v>
       </c>
@@ -17619,8 +18269,11 @@
       <c r="X199" s="10">
         <v>6.01</v>
       </c>
-    </row>
-    <row r="200" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y199" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
         <v>42552</v>
       </c>
@@ -17700,8 +18353,11 @@
       <c r="X200" s="8">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="201" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y200" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
         <v>42583</v>
       </c>
@@ -17781,8 +18437,11 @@
       <c r="X201" s="10">
         <v>5.44</v>
       </c>
-    </row>
-    <row r="202" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y201" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
         <v>42614</v>
       </c>
@@ -17862,8 +18521,11 @@
       <c r="X202" s="8">
         <v>5.07</v>
       </c>
-    </row>
-    <row r="203" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y202" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
         <v>42644</v>
       </c>
@@ -17943,8 +18605,11 @@
       <c r="X203" s="10">
         <v>4.87</v>
       </c>
-    </row>
-    <row r="204" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y203" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
         <v>42675</v>
       </c>
@@ -18024,8 +18689,11 @@
       <c r="X204" s="8">
         <v>4.8</v>
       </c>
-    </row>
-    <row r="205" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y204" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
         <v>42705</v>
       </c>
@@ -18105,8 +18773,11 @@
       <c r="X205" s="10">
         <v>4.6900000000000004</v>
       </c>
-    </row>
-    <row r="206" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y205" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
         <v>42736</v>
       </c>
@@ -18186,8 +18857,11 @@
       <c r="X206" s="8">
         <v>4.71</v>
       </c>
-    </row>
-    <row r="207" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y206" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
         <v>42767</v>
       </c>
@@ -18267,8 +18941,11 @@
       <c r="X207" s="10">
         <v>4.53</v>
       </c>
-    </row>
-    <row r="208" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y207" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
         <v>42795</v>
       </c>
@@ -18348,8 +19025,11 @@
       <c r="X208" s="8">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="209" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y208" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
         <v>42826</v>
       </c>
@@ -18429,8 +19109,11 @@
       <c r="X209" s="10">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="210" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y209" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
         <v>42856</v>
       </c>
@@ -18510,8 +19193,11 @@
       <c r="X210" s="8">
         <v>4.6399999999999997</v>
       </c>
-    </row>
-    <row r="211" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y210" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
         <v>42887</v>
       </c>
@@ -18591,8 +19277,11 @@
       <c r="X211" s="10">
         <v>4.12</v>
       </c>
-    </row>
-    <row r="212" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y211" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
         <v>42917</v>
       </c>
@@ -18672,8 +19361,11 @@
       <c r="X212" s="8">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="213" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y212" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
         <v>42948</v>
       </c>
@@ -18753,8 +19445,11 @@
       <c r="X213" s="10">
         <v>4.37</v>
       </c>
-    </row>
-    <row r="214" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y213" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
         <v>42979</v>
       </c>
@@ -18834,8 +19529,11 @@
       <c r="X214" s="8">
         <v>3.89</v>
       </c>
-    </row>
-    <row r="215" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y214" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
         <v>43009</v>
       </c>
@@ -18915,8 +19613,11 @@
       <c r="X215" s="10">
         <v>4.1399999999999997</v>
       </c>
-    </row>
-    <row r="216" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y215" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
         <v>43040</v>
       </c>
@@ -18996,8 +19697,11 @@
       <c r="X216" s="8">
         <v>3.99</v>
       </c>
-    </row>
-    <row r="217" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y216" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
         <v>43070</v>
       </c>
@@ -19077,8 +19781,11 @@
       <c r="X217" s="10">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="218" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y217" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
         <v>43101</v>
       </c>
@@ -19158,8 +19865,11 @@
       <c r="X218" s="8">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="219" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y218" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
         <v>43132</v>
       </c>
@@ -19239,8 +19949,11 @@
       <c r="X219" s="10">
         <v>3.92</v>
       </c>
-    </row>
-    <row r="220" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y219" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
         <v>43160</v>
       </c>
@@ -19320,8 +20033,11 @@
       <c r="X220" s="8">
         <v>3.86</v>
       </c>
-    </row>
-    <row r="221" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y220" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
         <v>43191</v>
       </c>
@@ -19401,8 +20117,11 @@
       <c r="X221" s="10">
         <v>4.07</v>
       </c>
-    </row>
-    <row r="222" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y221" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
         <v>43221</v>
       </c>
@@ -19482,8 +20201,11 @@
       <c r="X222" s="8">
         <v>4.3499999999999996</v>
       </c>
-    </row>
-    <row r="223" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y222" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
         <v>43252</v>
       </c>
@@ -19563,8 +20285,11 @@
       <c r="X223" s="10">
         <v>4.7699999999999996</v>
       </c>
-    </row>
-    <row r="224" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y223" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
         <v>43282</v>
       </c>
@@ -19644,8 +20369,11 @@
       <c r="X224" s="8">
         <v>3.74</v>
       </c>
-    </row>
-    <row r="225" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y224" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
         <v>43313</v>
       </c>
@@ -19725,8 +20453,11 @@
       <c r="X225" s="10">
         <v>3.65</v>
       </c>
-    </row>
-    <row r="226" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y225" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
         <v>43344</v>
       </c>
@@ -19806,8 +20537,11 @@
       <c r="X226" s="8">
         <v>4.1399999999999997</v>
       </c>
-    </row>
-    <row r="227" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y226" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
         <v>43374</v>
       </c>
@@ -19887,8 +20621,11 @@
       <c r="X227" s="10">
         <v>4.0199999999999996</v>
       </c>
-    </row>
-    <row r="228" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y227" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
         <v>43405</v>
       </c>
@@ -19968,8 +20705,11 @@
       <c r="X228" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="229" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y228" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
         <v>43435</v>
       </c>
@@ -20049,8 +20789,11 @@
       <c r="X229" s="10">
         <v>3.68</v>
       </c>
-    </row>
-    <row r="230" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y229" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
         <v>43466</v>
       </c>
@@ -20130,8 +20873,11 @@
       <c r="X230" s="8">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="231" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y230" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
         <v>43497</v>
       </c>
@@ -20211,8 +20957,11 @@
       <c r="X231" s="10">
         <v>3.94</v>
       </c>
-    </row>
-    <row r="232" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y231" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
         <v>43525</v>
       </c>
@@ -20292,8 +21041,11 @@
       <c r="X232" s="8">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="233" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y232" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
         <v>43556</v>
       </c>
@@ -20373,8 +21125,11 @@
       <c r="X233" s="10">
         <v>3.72</v>
       </c>
-    </row>
-    <row r="234" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y233" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
         <v>43586</v>
       </c>
@@ -20454,8 +21209,11 @@
       <c r="X234" s="8">
         <v>3.54</v>
       </c>
-    </row>
-    <row r="235" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y234" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
         <v>43617</v>
       </c>
@@ -20535,8 +21293,11 @@
       <c r="X235" s="10">
         <v>3.49</v>
       </c>
-    </row>
-    <row r="236" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y235" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
         <v>43647</v>
       </c>
@@ -20616,8 +21377,11 @@
       <c r="X236" s="8">
         <v>3.65</v>
       </c>
-    </row>
-    <row r="237" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y236" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
         <v>43678</v>
       </c>
@@ -20697,8 +21461,11 @@
       <c r="X237" s="10">
         <v>3.49</v>
       </c>
-    </row>
-    <row r="238" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y237" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
         <v>43709</v>
       </c>
@@ -20778,8 +21545,11 @@
       <c r="X238" s="8">
         <v>3.34</v>
       </c>
-    </row>
-    <row r="239" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y238" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
         <v>43739</v>
       </c>
@@ -20859,8 +21629,11 @@
       <c r="X239" s="10">
         <v>3.37</v>
       </c>
-    </row>
-    <row r="240" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y239" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
         <v>43770</v>
       </c>
@@ -20940,8 +21713,11 @@
       <c r="X240" s="8">
         <v>3.81</v>
       </c>
-    </row>
-    <row r="241" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y240" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
         <v>43800</v>
       </c>
@@ -21021,8 +21797,11 @@
       <c r="X241" s="10">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="242" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y241" s="22">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
         <v>43831</v>
       </c>
@@ -21102,8 +21881,11 @@
       <c r="X242" s="8">
         <v>3.44</v>
       </c>
-    </row>
-    <row r="243" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y242" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
         <v>43862</v>
       </c>
@@ -21183,8 +21965,11 @@
       <c r="X243" s="10">
         <v>3.46</v>
       </c>
-    </row>
-    <row r="244" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y243" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
         <v>43891</v>
       </c>
@@ -21264,8 +22049,11 @@
       <c r="X244" s="8">
         <v>3.13</v>
       </c>
-    </row>
-    <row r="245" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y244" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
         <v>43922</v>
       </c>
@@ -21345,8 +22133,11 @@
       <c r="X245" s="10">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="246" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y245" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
         <v>43952</v>
       </c>
@@ -21426,8 +22217,11 @@
       <c r="X246" s="8">
         <v>2.67</v>
       </c>
-    </row>
-    <row r="247" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y246" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
         <v>43983</v>
       </c>
@@ -21507,8 +22301,11 @@
       <c r="X247" s="10">
         <v>3.22</v>
       </c>
-    </row>
-    <row r="248" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y247" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
         <v>44013</v>
       </c>
@@ -21588,8 +22385,11 @@
       <c r="X248" s="8">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="249" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y248" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
         <v>44044</v>
       </c>
@@ -21669,8 +22469,11 @@
       <c r="X249" s="10">
         <v>3.14</v>
       </c>
-    </row>
-    <row r="250" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y249" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
         <v>44075</v>
       </c>
@@ -21750,8 +22553,11 @@
       <c r="X250" s="8">
         <v>3.37</v>
       </c>
-    </row>
-    <row r="251" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y250" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
         <v>44105</v>
       </c>
@@ -21831,8 +22637,11 @@
       <c r="X251" s="10">
         <v>3.92</v>
       </c>
-    </row>
-    <row r="252" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y251" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
         <v>44136</v>
       </c>
@@ -21912,8 +22721,11 @@
       <c r="X252" s="8">
         <v>4.1100000000000003</v>
       </c>
-    </row>
-    <row r="253" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y252" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
         <v>44166</v>
       </c>
@@ -21993,8 +22805,11 @@
       <c r="X253" s="10">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="254" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y253" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
         <v>44197</v>
       </c>
@@ -22074,8 +22889,11 @@
       <c r="X254" s="8">
         <v>3.57</v>
       </c>
-    </row>
-    <row r="255" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y254" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
         <v>44228</v>
       </c>
@@ -22155,8 +22973,11 @@
       <c r="X255" s="10">
         <v>3.99</v>
       </c>
-    </row>
-    <row r="256" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y255" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
         <v>44256</v>
       </c>
@@ -22236,8 +23057,11 @@
       <c r="X256" s="8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="257" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y256" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
         <v>44287</v>
       </c>
@@ -22317,8 +23141,11 @@
       <c r="X257" s="10">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="258" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y257" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
         <v>44317</v>
       </c>
@@ -22398,8 +23225,11 @@
       <c r="X258" s="8">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="259" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y258" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
         <v>44348</v>
       </c>
@@ -22479,8 +23309,11 @@
       <c r="X259" s="10">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="260" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y259" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
         <v>44378</v>
       </c>
@@ -22560,8 +23393,11 @@
       <c r="X260" s="8">
         <v>4.8899999999999997</v>
       </c>
-    </row>
-    <row r="261" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y260" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
         <v>44409</v>
       </c>
@@ -22641,8 +23477,11 @@
       <c r="X261" s="10">
         <v>4.82</v>
       </c>
-    </row>
-    <row r="262" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y261" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
         <v>44440</v>
       </c>
@@ -22722,8 +23561,11 @@
       <c r="X262" s="8">
         <v>5.35</v>
       </c>
-    </row>
-    <row r="263" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y262" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
         <v>44470</v>
       </c>
@@ -22803,8 +23645,11 @@
       <c r="X263" s="10">
         <v>5.51</v>
       </c>
-    </row>
-    <row r="264" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y263" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
         <v>44501</v>
       </c>
@@ -22884,8 +23729,11 @@
       <c r="X264" s="8">
         <v>5.89</v>
       </c>
-    </row>
-    <row r="265" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y264" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
         <v>44531</v>
       </c>
@@ -22965,8 +23813,11 @@
       <c r="X265" s="10">
         <v>5.23</v>
       </c>
-    </row>
-    <row r="266" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y265" s="22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
         <v>44562</v>
       </c>
@@ -23046,8 +23897,11 @@
       <c r="X266" s="8">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="267" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y266" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
         <v>44593</v>
       </c>
@@ -23127,8 +23981,11 @@
       <c r="X267" s="10">
         <v>5.46</v>
       </c>
-    </row>
-    <row r="268" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y267" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
         <v>44621</v>
       </c>
@@ -23208,8 +24065,11 @@
       <c r="X268" s="8">
         <v>6.27</v>
       </c>
-    </row>
-    <row r="269" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y268" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
         <v>44652</v>
       </c>
@@ -23289,8 +24149,11 @@
       <c r="X269" s="10">
         <v>6.01</v>
       </c>
-    </row>
-    <row r="270" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y269" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
         <v>44682</v>
       </c>
@@ -23370,8 +24233,11 @@
       <c r="X270" s="8">
         <v>6.19</v>
       </c>
-    </row>
-    <row r="271" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y270" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
         <v>44713</v>
       </c>
@@ -23451,8 +24317,11 @@
       <c r="X271" s="10">
         <v>5.76</v>
       </c>
-    </row>
-    <row r="272" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y271" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
         <v>44743</v>
       </c>
@@ -23532,8 +24401,11 @@
       <c r="X272" s="8">
         <v>4.76</v>
       </c>
-    </row>
-    <row r="273" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y272" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
         <v>44774</v>
       </c>
@@ -23613,8 +24485,11 @@
       <c r="X273" s="10">
         <v>5.18</v>
       </c>
-    </row>
-    <row r="274" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y273" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
         <v>44805</v>
       </c>
@@ -23694,8 +24569,11 @@
       <c r="X274" s="8">
         <v>4.74</v>
       </c>
-    </row>
-    <row r="275" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y274" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
         <v>44835</v>
       </c>
@@ -23775,8 +24653,11 @@
       <c r="X275" s="10">
         <v>5.14</v>
       </c>
-    </row>
-    <row r="276" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y275" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
         <v>44866</v>
       </c>
@@ -23856,8 +24737,11 @@
       <c r="X276" s="8">
         <v>5.37</v>
       </c>
-    </row>
-    <row r="277" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y276" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
         <v>44896</v>
       </c>
@@ -23937,8 +24821,11 @@
       <c r="X277" s="10">
         <v>5.26</v>
       </c>
-    </row>
-    <row r="278" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y277" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
         <v>44927</v>
       </c>
@@ -24018,8 +24905,11 @@
       <c r="X278" s="8">
         <v>5.71</v>
       </c>
-    </row>
-    <row r="279" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y278" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
         <v>44958</v>
       </c>
@@ -24099,8 +24989,11 @@
       <c r="X279" s="10">
         <v>5.77</v>
       </c>
-    </row>
-    <row r="280" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y279" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
         <v>44986</v>
       </c>
@@ -24180,8 +25073,11 @@
       <c r="X280" s="8">
         <v>5.55</v>
       </c>
-    </row>
-    <row r="281" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y280" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
         <v>45017</v>
       </c>
@@ -24261,8 +25157,11 @@
       <c r="X281" s="10">
         <v>5.28</v>
       </c>
-    </row>
-    <row r="282" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y281" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
         <v>45047</v>
       </c>
@@ -24342,8 +25241,11 @@
       <c r="X282" s="8">
         <v>4.6900000000000004</v>
       </c>
-    </row>
-    <row r="283" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y282" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
         <v>45078</v>
       </c>
@@ -24423,8 +25325,11 @@
       <c r="X283" s="10">
         <v>3.99</v>
       </c>
-    </row>
-    <row r="284" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y283" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
         <v>45108</v>
       </c>
@@ -24504,8 +25409,11 @@
       <c r="X284" s="8">
         <v>4.09</v>
       </c>
-    </row>
-    <row r="285" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y284" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
         <v>45139</v>
       </c>
@@ -24585,8 +25493,11 @@
       <c r="X285" s="10">
         <v>4.22</v>
       </c>
-    </row>
-    <row r="286" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y285" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
         <v>45170</v>
       </c>
@@ -24666,8 +25577,11 @@
       <c r="X286" s="8">
         <v>4.1100000000000003</v>
       </c>
-    </row>
-    <row r="287" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y286" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
         <v>45200</v>
       </c>
@@ -24747,8 +25661,11 @@
       <c r="X287" s="10">
         <v>3.92</v>
       </c>
-    </row>
-    <row r="288" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y287" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
         <v>45231</v>
       </c>
@@ -24828,8 +25745,11 @@
       <c r="X288" s="8">
         <v>3.92</v>
       </c>
-    </row>
-    <row r="289" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y288" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
         <v>45261</v>
       </c>
@@ -24909,8 +25829,11 @@
       <c r="X289" s="10">
         <v>3.81</v>
       </c>
-    </row>
-    <row r="290" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y289" s="22">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
         <v>45292</v>
       </c>
@@ -24990,8 +25913,11 @@
       <c r="X290" s="8">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="291" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y290" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
         <v>45323</v>
       </c>
@@ -25071,8 +25997,11 @@
       <c r="X291" s="10">
         <v>3.75</v>
       </c>
-    </row>
-    <row r="292" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y291" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
         <v>45352</v>
       </c>
@@ -25152,8 +26081,11 @@
       <c r="X292" s="8">
         <v>3.39</v>
       </c>
-    </row>
-    <row r="293" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y292" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
         <v>45383</v>
       </c>
@@ -25233,8 +26165,11 @@
       <c r="X293" s="10">
         <v>3.58</v>
       </c>
-    </row>
-    <row r="294" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y293" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
         <v>45413</v>
       </c>
@@ -25314,8 +26249,11 @@
       <c r="X294" s="8">
         <v>3.71</v>
       </c>
-    </row>
-    <row r="295" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y294" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
         <v>45444</v>
       </c>
@@ -25395,8 +26333,11 @@
       <c r="X295" s="10">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="296" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y295" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
         <v>45474</v>
       </c>
@@ -25476,8 +26417,11 @@
       <c r="X296" s="8">
         <v>3.84</v>
       </c>
-    </row>
-    <row r="297" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y296" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
         <v>45505</v>
       </c>
@@ -25557,8 +26501,11 @@
       <c r="X297" s="10">
         <v>3.79</v>
       </c>
-    </row>
-    <row r="298" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y297" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
         <v>45536</v>
       </c>
@@ -25638,8 +26585,11 @@
       <c r="X298" s="8">
         <v>4.13</v>
       </c>
-    </row>
-    <row r="299" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y298" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
         <v>45566</v>
       </c>
@@ -25719,8 +26669,11 @@
       <c r="X299" s="10">
         <v>4.1900000000000004</v>
       </c>
-    </row>
-    <row r="300" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y299" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
         <v>45597</v>
       </c>
@@ -25800,8 +26753,11 @@
       <c r="X300" s="8">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="301" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y300" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
         <v>45627</v>
       </c>
@@ -25881,8 +26837,11 @@
       <c r="X301" s="10">
         <v>4.99</v>
       </c>
-    </row>
-    <row r="302" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y301" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
         <v>45658</v>
       </c>
@@ -25962,8 +26921,11 @@
       <c r="X302" s="8">
         <v>5.47</v>
       </c>
-    </row>
-    <row r="303" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y302" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
         <v>45689</v>
       </c>
@@ -26043,8 +27005,11 @@
       <c r="X303" s="10">
         <v>5.89</v>
       </c>
-    </row>
-    <row r="304" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y303" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
         <v>45717</v>
       </c>
@@ -26124,8 +27089,11 @@
       <c r="X304" s="8">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="305" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y304" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
         <v>45748</v>
       </c>
@@ -26205,8 +27173,11 @@
       <c r="X305" s="10">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="306" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y305" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
         <v>45778</v>
       </c>
@@ -26286,8 +27257,11 @@
       <c r="X306" s="8">
         <v>4.8600000000000003</v>
       </c>
-    </row>
-    <row r="307" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y306" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
         <v>45809</v>
       </c>
@@ -26367,8 +27341,11 @@
       <c r="X307" s="10">
         <v>4.62</v>
       </c>
-    </row>
-    <row r="308" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y307" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
         <v>45839</v>
       </c>
@@ -26448,8 +27425,11 @@
       <c r="X308" s="8">
         <v>4.5199999999999996</v>
       </c>
-    </row>
-    <row r="309" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y308" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
         <v>45870</v>
       </c>
@@ -26529,8 +27509,11 @@
       <c r="X309" s="10">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="310" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y309" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
         <v>45901</v>
       </c>
@@ -26610,8 +27593,11 @@
       <c r="X310" s="8">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="311" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y310" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311" s="11"/>
       <c r="B311" s="11"/>
       <c r="C311" s="10">
@@ -26668,8 +27654,11 @@
       <c r="X311" s="10">
         <v>3.97</v>
       </c>
-    </row>
-    <row r="312" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y311" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312" s="11"/>
       <c r="B312" s="11"/>
       <c r="C312" s="11"/>
@@ -26718,8 +27707,11 @@
       <c r="X312" s="8">
         <v>4.0599999999999996</v>
       </c>
-    </row>
-    <row r="313" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y312" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313" s="11"/>
       <c r="B313" s="11"/>
       <c r="C313" s="11"/>
@@ -26748,8 +27740,11 @@
       <c r="X313" s="10">
         <v>3.97</v>
       </c>
-    </row>
-    <row r="314" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y313" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314" s="11"/>
       <c r="B314" s="11"/>
       <c r="C314" s="11"/>
@@ -26778,8 +27773,11 @@
       <c r="X314" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="315" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y314" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315" s="11"/>
       <c r="B315" s="11"/>
       <c r="C315" s="11"/>
@@ -26808,8 +27806,11 @@
       <c r="X315" s="10">
         <v>3.94</v>
       </c>
-    </row>
-    <row r="316" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y315" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316" s="11"/>
       <c r="B316" s="11"/>
       <c r="C316" s="11"/>
@@ -26838,8 +27839,11 @@
       <c r="X316" s="8">
         <v>4.2300000000000004</v>
       </c>
-    </row>
-    <row r="317" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="Y316" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317" s="11"/>
       <c r="B317" s="11"/>
       <c r="C317" s="11"/>
@@ -26866,8 +27870,11 @@
         <v>4.03</v>
       </c>
       <c r="X317" s="16"/>
-    </row>
-    <row r="318" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Y317" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="17"/>
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>

--- a/IPCA.xlsx
+++ b/IPCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\OneDrive\Documentos\TCC_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677B6293-DD65-4B94-84E0-0E53FE764BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71A7C80-05B0-483F-93F7-18B2B00565B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47E4BECD-C709-4E89-90ED-AD0720138F23}"/>
   </bookViews>
@@ -271,10 +271,10 @@
     <t>IPCA_Trans_nivel</t>
   </si>
   <si>
-    <t>espectativa_inflacao</t>
+    <t>meta_inflcao</t>
   </si>
   <si>
-    <t>meta_inflcao</t>
+    <t>expectativa_inflacao</t>
   </si>
 </sst>
 </file>
@@ -2425,7 +2425,7 @@
     <col min="22" max="22" width="21.6640625" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19.88671875" customWidth="1"/>
-    <col min="25" max="25" width="8.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5546875" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -2499,10 +2499,10 @@
         <v>12</v>
       </c>
       <c r="X1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y1" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="Y1" s="19" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">

--- a/IPCA.xlsx
+++ b/IPCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\OneDrive\Documentos\TCC_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71A7C80-05B0-483F-93F7-18B2B00565B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAEE284-22BE-4454-9D39-C139C456F9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47E4BECD-C709-4E89-90ED-AD0720138F23}"/>
   </bookViews>
@@ -274,7 +274,7 @@
     <t>meta_inflcao</t>
   </si>
   <si>
-    <t>expectativa_inflacao</t>
+    <t>Expectativa_inflacao</t>
   </si>
 </sst>
 </file>

--- a/IPCA.xlsx
+++ b/IPCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\OneDrive\Documentos\TCC_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAEE284-22BE-4454-9D39-C139C456F9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B201AD-F389-4E0E-9700-C61A972D946B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47E4BECD-C709-4E89-90ED-AD0720138F23}"/>
   </bookViews>
@@ -2424,7 +2424,7 @@
     <col min="21" max="21" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21.6640625" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.88671875" customWidth="1"/>
+    <col min="24" max="24" width="31.44140625" customWidth="1"/>
     <col min="25" max="25" width="13.5546875" style="21" customWidth="1"/>
   </cols>
   <sheetData>
